--- a/artfynd/A 24539-2025 artfynd.xlsx
+++ b/artfynd/A 24539-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102780777</v>
+        <v>55476332</v>
       </c>
       <c r="B2" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222771</v>
+        <v>220320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ängsskära</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Serratula tinctoria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,24 +705,24 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Priartorp, SV om, Srm</t>
+          <t>Hedlandet, S om Priartorp, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577749.8491182545</v>
+        <v>577799</v>
       </c>
       <c r="R2" t="n">
-        <v>6571673.901067232</v>
+        <v>6571755</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,22 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-07-31</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-06-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-07-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-06-19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,7 +768,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Betesmark, vid bryn</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -801,15 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>102780770</v>
+        <v>55476333</v>
       </c>
       <c r="B3" t="n">
-        <v>107008</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -836,7 +816,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -844,21 +824,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Priartorp, SV om, Srm</t>
+          <t>Hedlandet, S om Priartorp, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577639.3654998626</v>
+        <v>577809</v>
       </c>
       <c r="R3" t="n">
-        <v>6571742.696766499</v>
+        <v>6571745</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,22 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-07-31</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-06-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-07-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-06-19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,7 +879,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Skogsbryn, på stig</t>
+          <t>Betesmark, vid bryn</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -932,15 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>102780778</v>
+        <v>55476337</v>
       </c>
       <c r="B4" t="n">
-        <v>107008</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110117</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -967,7 +927,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -975,21 +935,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Priartorp, S om, Srm</t>
+          <t>Hedlandet, S om Priartorp, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577800.5278509903</v>
+        <v>577810</v>
       </c>
       <c r="R4" t="n">
-        <v>6571624.841026448</v>
+        <v>6571695</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1016,22 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-07-31</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-06-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-07-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-06-19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1045,7 +990,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Blandskog, vid stig</t>
+          <t>Betesmark, vid bryn</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1060,6 +1005,451 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>102780770</v>
+      </c>
+      <c r="B5" t="n">
+        <v>110117</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220320</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ängsskära</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Serratula tinctoria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Priartorp, SV om, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>577639</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6571743</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Gillberga</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-07-31</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-07-31</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Skogsbryn, på stig</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>102780778</v>
+      </c>
+      <c r="B6" t="n">
+        <v>110117</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220320</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ängsskära</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Serratula tinctoria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Priartorp, S om, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>577801</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6571625</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Gillberga</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-07-31</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-07-31</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Blandskog, vid stig</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>102780775</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Priartorp, SV om, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>577770</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6571704</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Gillberga</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-07-31</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-07-31</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>102780777</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Priartorp, SV om, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>577750</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6571674</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Gillberga</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-07-31</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-07-31</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24539-2025 artfynd.xlsx
+++ b/artfynd/A 24539-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55476332</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55476333</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55476337</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1121,6 +1141,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102780770</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1237,6 +1262,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102780778</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1339,6 +1369,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102780775</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1450,8 +1485,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102780777</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>